--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>56904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1385,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R9" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B10" t="n">
-        <v>56904</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,39 +1487,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R10" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129064868</v>
+        <v>129064585</v>
       </c>
       <c r="B12" t="n">
-        <v>91805</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,34 +1691,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603212</v>
+        <v>603273</v>
       </c>
       <c r="R12" t="n">
-        <v>7000140</v>
+        <v>7000010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129064585</v>
+        <v>129064868</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>91805</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,39 +1798,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603273</v>
+        <v>603212</v>
       </c>
       <c r="R13" t="n">
-        <v>7000010</v>
+        <v>7000140</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1858,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>129064083</v>
       </c>
       <c r="B6" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129064156</v>
       </c>
       <c r="B8" t="n">
-        <v>91721</v>
+        <v>91724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B9" t="n">
-        <v>56904</v>
+        <v>57883</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,39 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R9" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>56904</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,34 +1482,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R10" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129064585</v>
+        <v>129064868</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>91808</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,39 +1691,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603273</v>
+        <v>603212</v>
       </c>
       <c r="R12" t="n">
-        <v>7000010</v>
+        <v>7000140</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129064868</v>
+        <v>129064585</v>
       </c>
       <c r="B13" t="n">
-        <v>91805</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,34 +1788,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603212</v>
+        <v>603273</v>
       </c>
       <c r="R13" t="n">
-        <v>7000140</v>
+        <v>7000010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129064048</v>
+        <v>129064426</v>
       </c>
       <c r="B15" t="n">
-        <v>91520</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,34 +1996,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603316</v>
+        <v>603286</v>
       </c>
       <c r="R15" t="n">
-        <v>6999982</v>
+        <v>6999991</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,32 +2096,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129064426</v>
+        <v>129065105</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2115,26 +2129,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603286</v>
+        <v>603212</v>
       </c>
       <c r="R16" t="n">
-        <v>6999991</v>
+        <v>7000140</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,49 +2197,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129065105</v>
+        <v>129064048</v>
       </c>
       <c r="B17" t="n">
-        <v>98651</v>
+        <v>91523</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603212</v>
+        <v>603316</v>
       </c>
       <c r="R17" t="n">
-        <v>7000140</v>
+        <v>6999982</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,32 +2294,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129064460</v>
+        <v>129065507</v>
       </c>
       <c r="B18" t="n">
-        <v>91516</v>
+        <v>91724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603290</v>
+        <v>603304</v>
       </c>
       <c r="R18" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2391,32 +2391,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B19" t="n">
-        <v>91721</v>
+        <v>91519</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R19" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2491,7 +2491,7 @@
         <v>129064045</v>
       </c>
       <c r="B20" t="n">
-        <v>91805</v>
+        <v>91808</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>129064844</v>
       </c>
       <c r="B21" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>129064271</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>129064083</v>
       </c>
       <c r="B6" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129064439</v>
+        <v>129064156</v>
       </c>
       <c r="B7" t="n">
-        <v>91808</v>
+        <v>91727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603283</v>
+        <v>603290</v>
       </c>
       <c r="R7" t="n">
-        <v>7000003</v>
+        <v>6999981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129064156</v>
+        <v>129064439</v>
       </c>
       <c r="B8" t="n">
-        <v>91724</v>
+        <v>91811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603290</v>
+        <v>603283</v>
       </c>
       <c r="R8" t="n">
-        <v>6999981</v>
+        <v>7000003</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129064868</v>
+        <v>129064585</v>
       </c>
       <c r="B12" t="n">
-        <v>91808</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,34 +1691,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603212</v>
+        <v>603273</v>
       </c>
       <c r="R12" t="n">
-        <v>7000140</v>
+        <v>7000010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129064585</v>
+        <v>129064868</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,39 +1798,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603273</v>
+        <v>603212</v>
       </c>
       <c r="R13" t="n">
-        <v>7000010</v>
+        <v>7000140</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1858,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,10 +1985,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129064426</v>
+        <v>129064048</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>91526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,48 +1996,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603286</v>
+        <v>603316</v>
       </c>
       <c r="R15" t="n">
-        <v>6999991</v>
+        <v>6999982</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,32 +2082,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129065105</v>
+        <v>129064426</v>
       </c>
       <c r="B16" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2129,16 +2115,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603212</v>
+        <v>603286</v>
       </c>
       <c r="R16" t="n">
-        <v>7000140</v>
+        <v>6999991</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,45 +2193,49 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129064048</v>
+        <v>129065105</v>
       </c>
       <c r="B17" t="n">
-        <v>91523</v>
+        <v>98659</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603316</v>
+        <v>603212</v>
       </c>
       <c r="R17" t="n">
-        <v>6999982</v>
+        <v>7000140</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2297,7 +2297,7 @@
         <v>129065507</v>
       </c>
       <c r="B18" t="n">
-        <v>91724</v>
+        <v>91727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>129064460</v>
       </c>
       <c r="B19" t="n">
-        <v>91519</v>
+        <v>91522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>129064045</v>
       </c>
       <c r="B20" t="n">
-        <v>91808</v>
+        <v>91811</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>129064844</v>
       </c>
       <c r="B21" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>129064271</v>
       </c>
       <c r="B22" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129064156</v>
+        <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91727</v>
+        <v>91811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603290</v>
+        <v>603283</v>
       </c>
       <c r="R7" t="n">
-        <v>6999981</v>
+        <v>7000003</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129064439</v>
+        <v>129064156</v>
       </c>
       <c r="B8" t="n">
-        <v>91811</v>
+        <v>91727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603283</v>
+        <v>603290</v>
       </c>
       <c r="R8" t="n">
-        <v>7000003</v>
+        <v>6999981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B9" t="n">
-        <v>57883</v>
+        <v>56904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1385,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R9" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B10" t="n">
-        <v>56904</v>
+        <v>57883</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,39 +1487,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R10" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2585,45 +2585,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129064844</v>
+        <v>129064271</v>
       </c>
       <c r="B21" t="n">
-        <v>92226</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603212</v>
+        <v>603286</v>
       </c>
       <c r="R21" t="n">
-        <v>7000140</v>
+        <v>6999991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2682,49 +2686,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129064271</v>
+        <v>129064844</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>92226</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603286</v>
+        <v>603212</v>
       </c>
       <c r="R22" t="n">
-        <v>6999991</v>
+        <v>7000140</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129064585</v>
+        <v>129064868</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,39 +1691,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603273</v>
+        <v>603212</v>
       </c>
       <c r="R12" t="n">
-        <v>7000010</v>
+        <v>7000140</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129064868</v>
+        <v>129064585</v>
       </c>
       <c r="B13" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,34 +1788,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603212</v>
+        <v>603273</v>
       </c>
       <c r="R13" t="n">
-        <v>7000140</v>
+        <v>7000010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129064439</v>
+        <v>129064156</v>
       </c>
       <c r="B7" t="n">
-        <v>91811</v>
+        <v>91727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603283</v>
+        <v>603290</v>
       </c>
       <c r="R7" t="n">
-        <v>7000003</v>
+        <v>6999981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129064156</v>
+        <v>129064439</v>
       </c>
       <c r="B8" t="n">
-        <v>91727</v>
+        <v>91811</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603290</v>
+        <v>603283</v>
       </c>
       <c r="R8" t="n">
-        <v>6999981</v>
+        <v>7000003</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129064868</v>
+        <v>129064585</v>
       </c>
       <c r="B12" t="n">
-        <v>91811</v>
+        <v>57723</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,34 +1691,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603212</v>
+        <v>603273</v>
       </c>
       <c r="R12" t="n">
-        <v>7000140</v>
+        <v>7000010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129064585</v>
+        <v>129064868</v>
       </c>
       <c r="B13" t="n">
-        <v>57723</v>
+        <v>91811</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,39 +1798,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603273</v>
+        <v>603212</v>
       </c>
       <c r="R13" t="n">
-        <v>7000010</v>
+        <v>7000140</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1858,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2585,49 +2585,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129064271</v>
+        <v>129064844</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>92226</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603286</v>
+        <v>603212</v>
       </c>
       <c r="R21" t="n">
-        <v>6999991</v>
+        <v>7000140</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2686,45 +2682,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129064844</v>
+        <v>129064271</v>
       </c>
       <c r="B22" t="n">
-        <v>92226</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603212</v>
+        <v>603286</v>
       </c>
       <c r="R22" t="n">
-        <v>7000140</v>
+        <v>6999991</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>129064083</v>
       </c>
       <c r="B6" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129064156</v>
+        <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91727</v>
+        <v>91818</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603290</v>
+        <v>603283</v>
       </c>
       <c r="R7" t="n">
-        <v>6999981</v>
+        <v>7000003</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129064439</v>
+        <v>129064156</v>
       </c>
       <c r="B8" t="n">
-        <v>91811</v>
+        <v>91734</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603283</v>
+        <v>603290</v>
       </c>
       <c r="R8" t="n">
-        <v>7000003</v>
+        <v>6999981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B9" t="n">
-        <v>56904</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,39 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R9" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B10" t="n">
-        <v>57883</v>
+        <v>56906</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,34 +1482,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R10" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
         <v>129064173</v>
       </c>
       <c r="B11" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>129064585</v>
       </c>
       <c r="B12" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129064868</v>
       </c>
       <c r="B13" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>129064048</v>
       </c>
       <c r="B15" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>129064426</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>129065105</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>129065507</v>
       </c>
       <c r="B18" t="n">
-        <v>91727</v>
+        <v>91734</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>129064460</v>
       </c>
       <c r="B19" t="n">
-        <v>91522</v>
+        <v>91529</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>129064045</v>
       </c>
       <c r="B20" t="n">
-        <v>91811</v>
+        <v>91818</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>129064844</v>
       </c>
       <c r="B21" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>129064271</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -2294,32 +2294,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B18" t="n">
-        <v>91734</v>
+        <v>91529</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R18" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2391,32 +2391,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129064460</v>
+        <v>129065507</v>
       </c>
       <c r="B19" t="n">
-        <v>91529</v>
+        <v>91734</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603290</v>
+        <v>603304</v>
       </c>
       <c r="R19" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>129064083</v>
       </c>
       <c r="B6" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129064156</v>
       </c>
       <c r="B8" t="n">
-        <v>91734</v>
+        <v>91741</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129064868</v>
       </c>
       <c r="B13" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>129064048</v>
       </c>
       <c r="B15" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,32 +2082,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129064426</v>
+        <v>129065105</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>98676</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2115,26 +2115,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603286</v>
+        <v>603212</v>
       </c>
       <c r="R16" t="n">
-        <v>6999991</v>
+        <v>7000140</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,32 +2183,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129065105</v>
+        <v>129064426</v>
       </c>
       <c r="B17" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2226,16 +2216,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603212</v>
+        <v>603286</v>
       </c>
       <c r="R17" t="n">
-        <v>7000140</v>
+        <v>6999991</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,32 +2294,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129064460</v>
+        <v>129065507</v>
       </c>
       <c r="B18" t="n">
-        <v>91529</v>
+        <v>91741</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603290</v>
+        <v>603304</v>
       </c>
       <c r="R18" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2391,32 +2391,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B19" t="n">
-        <v>91734</v>
+        <v>91536</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R19" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2491,7 +2491,7 @@
         <v>129064045</v>
       </c>
       <c r="B20" t="n">
-        <v>91818</v>
+        <v>91825</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>129064844</v>
       </c>
       <c r="B21" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>129064271</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>129064083</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129064156</v>
       </c>
       <c r="B8" t="n">
-        <v>91741</v>
+        <v>91743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>56908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1385,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R9" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B10" t="n">
-        <v>56906</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,39 +1487,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R10" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1576,7 +1576,7 @@
         <v>129064173</v>
       </c>
       <c r="B11" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129064585</v>
+        <v>129064868</v>
       </c>
       <c r="B12" t="n">
-        <v>57725</v>
+        <v>91827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,39 +1691,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603273</v>
+        <v>603212</v>
       </c>
       <c r="R12" t="n">
-        <v>7000010</v>
+        <v>7000140</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129064868</v>
+        <v>129064585</v>
       </c>
       <c r="B13" t="n">
-        <v>91825</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,34 +1788,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603212</v>
+        <v>603273</v>
       </c>
       <c r="R13" t="n">
-        <v>7000140</v>
+        <v>7000010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>129064048</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2082,32 +2082,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129065105</v>
+        <v>129064426</v>
       </c>
       <c r="B16" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2115,16 +2115,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603212</v>
+        <v>603286</v>
       </c>
       <c r="R16" t="n">
-        <v>7000140</v>
+        <v>6999991</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,32 +2193,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129064426</v>
+        <v>129065105</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2216,26 +2226,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603286</v>
+        <v>603212</v>
       </c>
       <c r="R17" t="n">
-        <v>6999991</v>
+        <v>7000140</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2297,7 +2297,7 @@
         <v>129065507</v>
       </c>
       <c r="B18" t="n">
-        <v>91741</v>
+        <v>91743</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>129064460</v>
       </c>
       <c r="B19" t="n">
-        <v>91536</v>
+        <v>91538</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>129064045</v>
       </c>
       <c r="B20" t="n">
-        <v>91825</v>
+        <v>91827</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>129064844</v>
       </c>
       <c r="B21" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>129064271</v>
       </c>
       <c r="B22" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129064439</v>
+        <v>129064156</v>
       </c>
       <c r="B7" t="n">
-        <v>91827</v>
+        <v>91743</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603283</v>
+        <v>603290</v>
       </c>
       <c r="R7" t="n">
-        <v>7000003</v>
+        <v>6999981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129064156</v>
+        <v>129064439</v>
       </c>
       <c r="B8" t="n">
-        <v>91743</v>
+        <v>91827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603290</v>
+        <v>603283</v>
       </c>
       <c r="R8" t="n">
-        <v>6999981</v>
+        <v>7000003</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129064868</v>
+        <v>129064585</v>
       </c>
       <c r="B12" t="n">
-        <v>91827</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,34 +1691,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603212</v>
+        <v>603273</v>
       </c>
       <c r="R12" t="n">
-        <v>7000140</v>
+        <v>7000010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129064585</v>
+        <v>129064868</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>91827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,39 +1798,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603273</v>
+        <v>603212</v>
       </c>
       <c r="R13" t="n">
-        <v>7000010</v>
+        <v>7000140</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1858,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2082,32 +2082,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129064426</v>
+        <v>129065105</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2115,26 +2115,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603286</v>
+        <v>603212</v>
       </c>
       <c r="R16" t="n">
-        <v>6999991</v>
+        <v>7000140</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,10 +2183,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129065105</v>
+        <v>129065507</v>
       </c>
       <c r="B17" t="n">
-        <v>98678</v>
+        <v>91743</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2204,38 +2194,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>48</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603212</v>
+        <v>603304</v>
       </c>
       <c r="R17" t="n">
-        <v>7000140</v>
+        <v>6999982</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,32 +2280,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B18" t="n">
-        <v>91743</v>
+        <v>91538</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2329,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R18" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2354,7 +2340,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2391,10 +2377,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129064460</v>
+        <v>129064045</v>
       </c>
       <c r="B19" t="n">
-        <v>91538</v>
+        <v>91827</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2402,21 +2388,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2426,10 +2412,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603290</v>
+        <v>603316</v>
       </c>
       <c r="R19" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2451,7 +2437,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -2488,45 +2474,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129064045</v>
+        <v>129064271</v>
       </c>
       <c r="B20" t="n">
-        <v>91827</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603316</v>
+        <v>603286</v>
       </c>
       <c r="R20" t="n">
-        <v>6999982</v>
+        <v>6999991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2682,37 +2672,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129064271</v>
+        <v>129064426</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129064156</v>
+        <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91743</v>
+        <v>91827</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603290</v>
+        <v>603283</v>
       </c>
       <c r="R7" t="n">
-        <v>6999981</v>
+        <v>7000003</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129064439</v>
+        <v>129064156</v>
       </c>
       <c r="B8" t="n">
-        <v>91827</v>
+        <v>91743</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603283</v>
+        <v>603290</v>
       </c>
       <c r="R8" t="n">
-        <v>7000003</v>
+        <v>6999981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>129064083</v>
       </c>
       <c r="B6" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129064156</v>
       </c>
       <c r="B8" t="n">
-        <v>91743</v>
+        <v>91752</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>129064868</v>
       </c>
       <c r="B13" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>129064048</v>
       </c>
       <c r="B15" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>129065105</v>
       </c>
       <c r="B16" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B17" t="n">
-        <v>91743</v>
+        <v>91536</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R17" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129064460</v>
+        <v>129065507</v>
       </c>
       <c r="B18" t="n">
-        <v>91538</v>
+        <v>91752</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603290</v>
+        <v>603304</v>
       </c>
       <c r="R18" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2380,7 +2380,7 @@
         <v>129064045</v>
       </c>
       <c r="B19" t="n">
-        <v>91827</v>
+        <v>91837</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>129064271</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>129064844</v>
       </c>
       <c r="B21" t="n">
-        <v>92242</v>
+        <v>92257</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129064156</v>
       </c>
       <c r="B8" t="n">
-        <v>91752</v>
+        <v>91753</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B9" t="n">
-        <v>56908</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,39 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R9" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>56908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,34 +1482,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R10" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129064585</v>
+        <v>129064868</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>91838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,39 +1691,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603273</v>
+        <v>603212</v>
       </c>
       <c r="R12" t="n">
-        <v>7000010</v>
+        <v>7000140</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1756,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1787,10 +1777,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129064868</v>
+        <v>129064585</v>
       </c>
       <c r="B13" t="n">
-        <v>91837</v>
+        <v>57727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1798,34 +1788,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603212</v>
+        <v>603273</v>
       </c>
       <c r="R13" t="n">
-        <v>7000140</v>
+        <v>7000010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1858,6 +1853,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,45 +1985,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129064048</v>
+        <v>129065105</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603316</v>
+        <v>603212</v>
       </c>
       <c r="R15" t="n">
-        <v>6999982</v>
+        <v>7000140</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,49 +2086,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129065105</v>
+        <v>129064048</v>
       </c>
       <c r="B16" t="n">
-        <v>98704</v>
+        <v>91540</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603212</v>
+        <v>603316</v>
       </c>
       <c r="R16" t="n">
-        <v>7000140</v>
+        <v>6999982</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2283,7 +2283,7 @@
         <v>129065507</v>
       </c>
       <c r="B18" t="n">
-        <v>91752</v>
+        <v>91753</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>129064045</v>
       </c>
       <c r="B19" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>129064271</v>
       </c>
       <c r="B20" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>129064844</v>
       </c>
       <c r="B21" t="n">
-        <v>92257</v>
+        <v>92258</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>56908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1385,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R9" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B10" t="n">
-        <v>56908</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,39 +1487,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R10" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,49 +1985,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129065105</v>
+        <v>129064048</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>91540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603212</v>
+        <v>603316</v>
       </c>
       <c r="R15" t="n">
-        <v>7000140</v>
+        <v>6999982</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,45 +2082,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129064048</v>
+        <v>129065105</v>
       </c>
       <c r="B16" t="n">
-        <v>91540</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603316</v>
+        <v>603212</v>
       </c>
       <c r="R16" t="n">
-        <v>6999982</v>
+        <v>7000140</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129064460</v>
+        <v>129065507</v>
       </c>
       <c r="B17" t="n">
-        <v>91536</v>
+        <v>91753</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603290</v>
+        <v>603304</v>
       </c>
       <c r="R17" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B18" t="n">
-        <v>91753</v>
+        <v>91536</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R18" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2474,49 +2474,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129064271</v>
+        <v>129064844</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>92258</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603286</v>
+        <v>603212</v>
       </c>
       <c r="R20" t="n">
-        <v>6999991</v>
+        <v>7000140</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2575,45 +2571,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129064844</v>
+        <v>129064271</v>
       </c>
       <c r="B21" t="n">
-        <v>92258</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603212</v>
+        <v>603286</v>
       </c>
       <c r="R21" t="n">
-        <v>7000140</v>
+        <v>6999991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>129064083</v>
       </c>
       <c r="B6" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129064439</v>
+        <v>129064156</v>
       </c>
       <c r="B7" t="n">
-        <v>91838</v>
+        <v>91756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603283</v>
+        <v>603290</v>
       </c>
       <c r="R7" t="n">
-        <v>7000003</v>
+        <v>6999981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129064156</v>
+        <v>129064439</v>
       </c>
       <c r="B8" t="n">
-        <v>91753</v>
+        <v>91841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603290</v>
+        <v>603283</v>
       </c>
       <c r="R8" t="n">
-        <v>6999981</v>
+        <v>7000003</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1683,7 +1683,7 @@
         <v>129064868</v>
       </c>
       <c r="B12" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,45 +1985,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129064048</v>
+        <v>129065105</v>
       </c>
       <c r="B15" t="n">
-        <v>91540</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603316</v>
+        <v>603212</v>
       </c>
       <c r="R15" t="n">
-        <v>6999982</v>
+        <v>7000140</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2082,49 +2086,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129065105</v>
+        <v>129064048</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>91543</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603212</v>
+        <v>603316</v>
       </c>
       <c r="R16" t="n">
-        <v>7000140</v>
+        <v>6999982</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B17" t="n">
-        <v>91753</v>
+        <v>91539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R17" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129064460</v>
+        <v>129065507</v>
       </c>
       <c r="B18" t="n">
-        <v>91536</v>
+        <v>91756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603290</v>
+        <v>603304</v>
       </c>
       <c r="R18" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2380,7 +2380,7 @@
         <v>129064045</v>
       </c>
       <c r="B19" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>129064844</v>
       </c>
       <c r="B20" t="n">
-        <v>92258</v>
+        <v>92261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>129064271</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>129064083</v>
       </c>
       <c r="B6" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129064156</v>
+        <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91756</v>
+        <v>91843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603290</v>
+        <v>603283</v>
       </c>
       <c r="R7" t="n">
-        <v>6999981</v>
+        <v>7000003</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129064439</v>
+        <v>129064156</v>
       </c>
       <c r="B8" t="n">
-        <v>91841</v>
+        <v>91758</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603283</v>
+        <v>603290</v>
       </c>
       <c r="R8" t="n">
-        <v>7000003</v>
+        <v>6999981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1683,7 +1683,7 @@
         <v>129064868</v>
       </c>
       <c r="B12" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>129065105</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2089,7 +2089,7 @@
         <v>129064048</v>
       </c>
       <c r="B16" t="n">
-        <v>91543</v>
+        <v>91545</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129064460</v>
+        <v>129065507</v>
       </c>
       <c r="B17" t="n">
-        <v>91539</v>
+        <v>91758</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603290</v>
+        <v>603304</v>
       </c>
       <c r="R17" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B18" t="n">
-        <v>91756</v>
+        <v>91541</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R18" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2380,7 +2380,7 @@
         <v>129064045</v>
       </c>
       <c r="B19" t="n">
-        <v>91841</v>
+        <v>91843</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>129064844</v>
       </c>
       <c r="B20" t="n">
-        <v>92261</v>
+        <v>92263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>129064271</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>129064083</v>
       </c>
       <c r="B6" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129064439</v>
+        <v>129064156</v>
       </c>
       <c r="B7" t="n">
-        <v>91843</v>
+        <v>91762</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603283</v>
+        <v>603290</v>
       </c>
       <c r="R7" t="n">
-        <v>7000003</v>
+        <v>6999981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129064156</v>
+        <v>129064439</v>
       </c>
       <c r="B8" t="n">
-        <v>91758</v>
+        <v>91847</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603290</v>
+        <v>603283</v>
       </c>
       <c r="R8" t="n">
-        <v>6999981</v>
+        <v>7000003</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B9" t="n">
-        <v>56908</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,39 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R9" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>56908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,34 +1482,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R10" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1683,7 @@
         <v>129064868</v>
       </c>
       <c r="B12" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,49 +1985,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129065105</v>
+        <v>129064048</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>91549</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603212</v>
+        <v>603316</v>
       </c>
       <c r="R15" t="n">
-        <v>7000140</v>
+        <v>6999982</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2086,45 +2082,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129064048</v>
+        <v>129065105</v>
       </c>
       <c r="B16" t="n">
-        <v>91545</v>
+        <v>98716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603316</v>
+        <v>603212</v>
       </c>
       <c r="R16" t="n">
-        <v>6999982</v>
+        <v>7000140</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B17" t="n">
-        <v>91758</v>
+        <v>91545</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R17" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129064460</v>
+        <v>129065507</v>
       </c>
       <c r="B18" t="n">
-        <v>91541</v>
+        <v>91762</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603290</v>
+        <v>603304</v>
       </c>
       <c r="R18" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2380,7 +2380,7 @@
         <v>129064045</v>
       </c>
       <c r="B19" t="n">
-        <v>91843</v>
+        <v>91847</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2474,45 +2474,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129064844</v>
+        <v>129064271</v>
       </c>
       <c r="B20" t="n">
-        <v>92263</v>
+        <v>98716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603212</v>
+        <v>603286</v>
       </c>
       <c r="R20" t="n">
-        <v>7000140</v>
+        <v>6999991</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2571,49 +2575,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129064271</v>
+        <v>129064844</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>92267</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603286</v>
+        <v>603212</v>
       </c>
       <c r="R21" t="n">
-        <v>6999991</v>
+        <v>7000140</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>129064083</v>
       </c>
       <c r="B6" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129064156</v>
+        <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91762</v>
+        <v>91848</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1215,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603290</v>
+        <v>603283</v>
       </c>
       <c r="R7" t="n">
-        <v>6999981</v>
+        <v>7000003</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1277,32 +1277,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129064439</v>
+        <v>129064156</v>
       </c>
       <c r="B8" t="n">
-        <v>91847</v>
+        <v>91763</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603283</v>
+        <v>603290</v>
       </c>
       <c r="R8" t="n">
-        <v>7000003</v>
+        <v>6999981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>56908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1385,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R9" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B10" t="n">
-        <v>56908</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,39 +1487,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R10" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1683,7 @@
         <v>129064868</v>
       </c>
       <c r="B12" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>129064048</v>
       </c>
       <c r="B15" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>129065105</v>
       </c>
       <c r="B16" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129064460</v>
+        <v>129065507</v>
       </c>
       <c r="B17" t="n">
-        <v>91545</v>
+        <v>91763</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603290</v>
+        <v>603304</v>
       </c>
       <c r="R17" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B18" t="n">
-        <v>91762</v>
+        <v>91546</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R18" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2380,7 +2380,7 @@
         <v>129064045</v>
       </c>
       <c r="B19" t="n">
-        <v>91847</v>
+        <v>91848</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>129064271</v>
       </c>
       <c r="B20" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         <v>129064844</v>
       </c>
       <c r="B21" t="n">
-        <v>92267</v>
+        <v>92268</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B9" t="n">
-        <v>56908</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,39 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R9" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>56908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,34 +1482,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R10" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2474,49 +2474,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129064271</v>
+        <v>129064844</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>92268</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603286</v>
+        <v>603212</v>
       </c>
       <c r="R20" t="n">
-        <v>6999991</v>
+        <v>7000140</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2575,45 +2571,49 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129064844</v>
+        <v>129064271</v>
       </c>
       <c r="B21" t="n">
-        <v>92268</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>603212</v>
+        <v>603286</v>
       </c>
       <c r="R21" t="n">
-        <v>7000140</v>
+        <v>6999991</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>56908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1385,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R9" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B10" t="n">
-        <v>56908</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,39 +1487,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R10" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>129064083</v>
       </c>
       <c r="B6" t="n">
-        <v>91514</v>
+        <v>91517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>129064156</v>
       </c>
       <c r="B8" t="n">
-        <v>91763</v>
+        <v>91766</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>129064868</v>
       </c>
       <c r="B12" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129064276</v>
       </c>
       <c r="B14" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>129064048</v>
       </c>
       <c r="B15" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>129065105</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>129065507</v>
       </c>
       <c r="B17" t="n">
-        <v>91763</v>
+        <v>91766</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>129064460</v>
       </c>
       <c r="B18" t="n">
-        <v>91546</v>
+        <v>91549</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>129064045</v>
       </c>
       <c r="B19" t="n">
-        <v>91848</v>
+        <v>91851</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>129064844</v>
       </c>
       <c r="B20" t="n">
-        <v>92268</v>
+        <v>92271</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
         <v>129064271</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -2183,32 +2183,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B17" t="n">
-        <v>91766</v>
+        <v>91549</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R17" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129064460</v>
+        <v>129065507</v>
       </c>
       <c r="B18" t="n">
-        <v>91549</v>
+        <v>91766</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603290</v>
+        <v>603304</v>
       </c>
       <c r="R18" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B9" t="n">
-        <v>56908</v>
+        <v>57887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,39 +1385,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R9" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1476,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>56908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,34 +1482,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R10" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2183,32 +2183,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129064460</v>
+        <v>129065507</v>
       </c>
       <c r="B17" t="n">
-        <v>91549</v>
+        <v>91766</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1108</v>
+        <v>48</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2218,10 +2218,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603290</v>
+        <v>603304</v>
       </c>
       <c r="R17" t="n">
-        <v>6999981</v>
+        <v>6999982</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -2280,32 +2280,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129065507</v>
+        <v>129064460</v>
       </c>
       <c r="B18" t="n">
-        <v>91766</v>
+        <v>91549</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2315,10 +2315,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603304</v>
+        <v>603290</v>
       </c>
       <c r="R18" t="n">
-        <v>6999982</v>
+        <v>6999981</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -1374,10 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129064734</v>
+        <v>129065354</v>
       </c>
       <c r="B9" t="n">
-        <v>57887</v>
+        <v>56908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,34 +1385,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603193</v>
+        <v>603286</v>
       </c>
       <c r="R9" t="n">
-        <v>7000100</v>
+        <v>6999991</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1471,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129065354</v>
+        <v>129064734</v>
       </c>
       <c r="B10" t="n">
-        <v>56908</v>
+        <v>57887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,39 +1487,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603286</v>
+        <v>603193</v>
       </c>
       <c r="R10" t="n">
-        <v>6999991</v>
+        <v>7000100</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1680,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129064868</v>
+        <v>129064585</v>
       </c>
       <c r="B12" t="n">
-        <v>91851</v>
+        <v>57727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1691,34 +1691,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603212</v>
+        <v>603273</v>
       </c>
       <c r="R12" t="n">
-        <v>7000140</v>
+        <v>7000010</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,6 +1756,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,10 +1787,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129064585</v>
+        <v>129064868</v>
       </c>
       <c r="B13" t="n">
-        <v>57727</v>
+        <v>91851</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1788,39 +1798,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603273</v>
+        <v>603212</v>
       </c>
       <c r="R13" t="n">
-        <v>7000010</v>
+        <v>7000140</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1853,11 +1858,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -2675,7 +2675,7 @@
         <v>129064426</v>
       </c>
       <c r="B22" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -2675,7 +2675,7 @@
         <v>129064426</v>
       </c>
       <c r="B22" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -2675,7 +2675,7 @@
         <v>129064426</v>
       </c>
       <c r="B22" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118853568</v>
+        <v>129064156</v>
       </c>
       <c r="B2" t="n">
-        <v>91445</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bäckingesbäcken, Ång</t>
+          <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603195</v>
+        <v>603290</v>
       </c>
       <c r="R2" t="n">
-        <v>7000058</v>
+        <v>6999981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,17 +735,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,62 +760,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118853570</v>
+        <v>129065507</v>
       </c>
       <c r="B3" t="n">
-        <v>90797</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäckingesbäcken, Ång</t>
+          <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603292</v>
+        <v>603304</v>
       </c>
       <c r="R3" t="n">
-        <v>7000015</v>
+        <v>6999982</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2025-10-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maria Wallin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118853567</v>
+        <v>118853569</v>
       </c>
       <c r="B4" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>620</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogsfru</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Epipogium aphyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603200</v>
+        <v>603195</v>
       </c>
       <c r="R4" t="n">
-        <v>7000034</v>
+        <v>7000058</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118853569</v>
+        <v>118853570</v>
       </c>
       <c r="B5" t="n">
-        <v>97856</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>620</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsfru</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipogium aphyllum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603195</v>
+        <v>603292</v>
       </c>
       <c r="R5" t="n">
-        <v>7000058</v>
+        <v>7000015</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129064083</v>
+        <v>129064045</v>
       </c>
       <c r="B6" t="n">
-        <v>91517</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1121,7 +1101,7 @@
         <v>603316</v>
       </c>
       <c r="R6" t="n">
-        <v>6999995</v>
+        <v>6999982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1183,7 +1163,7 @@
         <v>129064439</v>
       </c>
       <c r="B7" t="n">
-        <v>91851</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1277,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129064156</v>
+        <v>129064868</v>
       </c>
       <c r="B8" t="n">
-        <v>91766</v>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603290</v>
+        <v>603212</v>
       </c>
       <c r="R8" t="n">
-        <v>6999981</v>
+        <v>7000140</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1317,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1374,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129065354</v>
+        <v>129064460</v>
       </c>
       <c r="B9" t="n">
-        <v>56908</v>
+        <v>91905</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,39 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603286</v>
+        <v>603290</v>
       </c>
       <c r="R9" t="n">
-        <v>6999991</v>
+        <v>6999981</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,7 +1414,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1476,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129064734</v>
+        <v>129064048</v>
       </c>
       <c r="B10" t="n">
-        <v>57887</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603193</v>
+        <v>603316</v>
       </c>
       <c r="R10" t="n">
-        <v>7000100</v>
+        <v>6999982</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1573,50 +1548,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129064173</v>
+        <v>129064844</v>
       </c>
       <c r="B11" t="n">
-        <v>57727</v>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603310</v>
+        <v>603212</v>
       </c>
       <c r="R11" t="n">
-        <v>6999987</v>
+        <v>7000140</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,11 +1619,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,50 +1645,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129064585</v>
+        <v>118853568</v>
       </c>
       <c r="B12" t="n">
-        <v>57727</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hällberget, Ång</t>
+          <t>Bäckingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>603273</v>
+        <v>603195</v>
       </c>
       <c r="R12" t="n">
-        <v>7000010</v>
+        <v>7000058</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1750,17 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1775,44 +1730,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129064868</v>
+        <v>129064083</v>
       </c>
       <c r="B13" t="n">
-        <v>91851</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1822,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>603212</v>
+        <v>603316</v>
       </c>
       <c r="R13" t="n">
-        <v>7000140</v>
+        <v>6999995</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1884,37 +1839,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129064276</v>
+        <v>129064173</v>
       </c>
       <c r="B14" t="n">
-        <v>98727</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1923,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>603290</v>
+        <v>603310</v>
       </c>
       <c r="R14" t="n">
-        <v>6999981</v>
+        <v>6999987</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1948,7 +1904,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1959,6 +1915,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1985,10 +1946,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129064048</v>
+        <v>129064259</v>
       </c>
       <c r="B15" t="n">
-        <v>91553</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1996,34 +1957,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>603316</v>
+        <v>603282</v>
       </c>
       <c r="R15" t="n">
-        <v>6999982</v>
+        <v>6999974</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2045,7 +2011,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2056,6 +2022,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2082,32 +2053,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129065105</v>
+        <v>129064426</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2115,16 +2086,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>603212</v>
+        <v>603286</v>
       </c>
       <c r="R16" t="n">
-        <v>7000140</v>
+        <v>6999991</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2183,45 +2164,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129065507</v>
+        <v>129064585</v>
       </c>
       <c r="B17" t="n">
-        <v>91766</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>603304</v>
+        <v>603273</v>
       </c>
       <c r="R17" t="n">
-        <v>6999982</v>
+        <v>7000010</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2254,6 +2240,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2280,45 +2271,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129064460</v>
+        <v>129065354</v>
       </c>
       <c r="B18" t="n">
-        <v>91549</v>
+        <v>57132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Hällberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>603290</v>
+        <v>603286</v>
       </c>
       <c r="R18" t="n">
-        <v>6999981</v>
+        <v>6999991</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,7 +2336,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Graninge</t>
+          <t>Långsele</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -2377,10 +2373,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129064045</v>
+        <v>129064734</v>
       </c>
       <c r="B19" t="n">
-        <v>91851</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2388,21 +2384,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2412,10 +2408,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>603316</v>
+        <v>603193</v>
       </c>
       <c r="R19" t="n">
-        <v>6999982</v>
+        <v>7000100</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,45 +2470,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129064844</v>
+        <v>118853567</v>
       </c>
       <c r="B20" t="n">
-        <v>92271</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hällberget, Ång</t>
+          <t>Bäckingesbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>603212</v>
+        <v>603200</v>
       </c>
       <c r="R20" t="n">
-        <v>7000140</v>
+        <v>7000034</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2539,12 +2535,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2559,12 +2555,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Maria Wallin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2574,7 +2570,7 @@
         <v>129064271</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2672,47 +2668,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129064426</v>
+        <v>129064276</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2721,10 +2707,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>603286</v>
+        <v>603290</v>
       </c>
       <c r="R22" t="n">
-        <v>6999991</v>
+        <v>6999981</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2746,7 +2732,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Långsele</t>
+          <t>Graninge</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -2780,6 +2766,107 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129065105</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Hällberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>603212</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7000140</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Långsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-12</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44735-2025 artfynd.xlsx
+++ b/artfynd/A 44735-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064156</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129065507</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118853569</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118853570</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064045</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064439</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064868</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064460</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064048</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064844</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118853568</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064083</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064173</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064259</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2161,6 +2236,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064426</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2268,6 +2348,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064585</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2370,6 +2455,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129065354</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2467,6 +2557,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064734</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2564,6 +2659,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118853567</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2665,6 +2765,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064271</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2766,6 +2871,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064276</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2867,8 +2977,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129065105</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>